--- a/jpcore-r4/feature/wg45-FamilyMember/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/wg45-FamilyMember/StructureDefinition-jp-familymemberhistory.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="335">
   <si>
     <t>Property</t>
   </si>
@@ -429,21 +429,21 @@
     <t>FamilyMemberHistory.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -453,31 +453,7 @@
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.extension:SiblingOrder</t>
-  </si>
-  <si>
-    <t>SiblingOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_FamilyMemberHistory_SiblingOrder}
-</t>
-  </si>
-  <si>
-    <t>同胞内出生順</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistoryのrelationship（続柄）と組み合わせて、関連する家族構成員の同胞内出生順と性別同胞内出生順名称を表現する拡張。同胞内の順位を整数で、性別の同胞内の出生順の名称（長男、長女、次男、次女など）をCodeableConceptで表現する。日常の臨床では家族の氏名は聴取されずに続柄で記述され、また、関係者全員の生年月日や年齢を聴取できない場合が多いことを想定している。また、遺伝学的血統図は対象外である。本実装ガイド（Version 1.2.0）の範囲外であるが、 参考として[Genetic Pedigreeプロファイル](https://hl7.org/fhir/R4/familymemberhistory-genetic.html)を参照すること。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>FamilyMemberHistory.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
@@ -488,9 +464,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -702,6 +675,108 @@
     <t>code</t>
   </si>
   <si>
+    <t>FamilyMemberHistory.relationship.id</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.relationship.extension</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.relationship.extension:SiblingOrder</t>
+  </si>
+  <si>
+    <t>SiblingOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_FamilyMemberHistory_SiblingOrder}
+</t>
+  </si>
+  <si>
+    <t>同胞内出生順</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistoryのrelationship（続柄）と組み合わせて、関連する家族構成員の同胞内出生順と性別同胞内出生順名称を表現する拡張。同胞内の順位を整数で、性別の同胞内の出生順の名称（長男、長女、次男、次女など）をCodeableConceptで表現する。日常の臨床では家族の氏名は聴取されずに続柄で記述され、また、関係者全員の生年月日や年齢を聴取できない場合が多いことを想定している。また、遺伝学的血統図は対象外である。本実装ガイド（Version 1.2.0）の範囲外であるが、 参考として[Genetic Pedigreeプロファイル](https://hl7.org/fhir/R4/familymemberhistory-genetic.html)を参照すること。</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.relationship.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.relationship.text</t>
+  </si>
+  <si>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
     <t>FamilyMemberHistory.sex</t>
   </si>
   <si>
@@ -891,28 +966,7 @@
     <t>FamilyMemberHistory.condition.id</t>
   </si>
   <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>FamilyMemberHistory.condition.extension</t>
-  </si>
-  <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>FamilyMemberHistory.condition.modifierExtension</t>
@@ -1307,10 +1361,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AN41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.19140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.4375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.19140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1338,7 +1392,7 @@
     <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="42.19140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -1346,7 +1400,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="161.19921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -2276,7 +2330,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2295,15 +2349,17 @@
         <v>78</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>78</v>
@@ -2340,14 +2396,16 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>139</v>
@@ -2371,7 +2429,7 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2382,41 +2440,43 @@
         <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
       </c>
@@ -2464,7 +2524,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2473,7 +2533,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>140</v>
@@ -2485,7 +2545,7 @@
         <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -2493,14 +2553,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2513,25 +2573,25 @@
         <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="J11" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>78</v>
@@ -2580,7 +2640,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2592,27 +2652,27 @@
         <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2635,20 +2695,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>78</v>
       </c>
@@ -2696,7 +2752,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2711,24 +2767,24 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2751,15 +2807,17 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>78</v>
@@ -2808,7 +2866,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2823,13 +2881,13 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -2837,10 +2895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2848,31 +2906,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2898,13 +2956,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -2922,13 +2980,13 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>78</v>
@@ -2943,18 +3001,18 @@
         <v>78</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2962,7 +3020,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>89</v>
@@ -2971,24 +3029,24 @@
         <v>78</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>78</v>
       </c>
@@ -3012,13 +3070,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -3036,10 +3094,10 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>89</v>
@@ -3051,32 +3109,32 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>182</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>89</v>
@@ -3091,18 +3149,16 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N16" s="2"/>
-      <c r="O16" t="s" s="2">
-        <v>187</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>78</v>
       </c>
@@ -3126,13 +3182,13 @@
         <v>78</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>78</v>
@@ -3150,10 +3206,10 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>89</v>
@@ -3165,16 +3221,16 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>78</v>
+        <v>189</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -3186,11 +3242,11 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>89</v>
@@ -3205,16 +3261,20 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+      <c r="O17" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>78</v>
       </c>
@@ -3265,7 +3325,7 @@
         <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>89</v>
@@ -3277,7 +3337,7 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>78</v>
@@ -3325,11 +3385,9 @@
       <c r="M18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="N18" s="2"/>
+      <c r="O18" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3399,18 +3457,18 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3418,7 +3476,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -3433,18 +3491,16 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
@@ -3468,13 +3524,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3492,10 +3548,10 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>89</v>
@@ -3513,7 +3569,7 @@
         <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -3521,10 +3577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3532,7 +3588,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -3544,16 +3600,16 @@
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3580,13 +3636,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -3604,10 +3660,10 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>89</v>
@@ -3616,7 +3672,7 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -3625,7 +3681,7 @@
         <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
@@ -3633,21 +3689,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>78</v>
@@ -3656,23 +3712,21 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
       </c>
@@ -3696,43 +3750,43 @@
         <v>78</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
@@ -3741,7 +3795,7 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -3749,12 +3803,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
       </c>
@@ -3775,18 +3831,16 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>78</v>
       </c>
@@ -3834,19 +3888,19 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>78</v>
@@ -3855,7 +3909,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -3863,10 +3917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3877,7 +3931,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>78</v>
@@ -3889,19 +3943,19 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -3950,16 +4004,16 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>101</v>
@@ -3968,10 +4022,10 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -3979,10 +4033,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4005,26 +4059,24 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q24" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
         <v>78</v>
       </c>
@@ -4077,7 +4129,7 @@
         <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>101</v>
@@ -4086,10 +4138,10 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4097,10 +4149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4123,16 +4175,20 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
       </c>
@@ -4156,13 +4212,13 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
@@ -4180,7 +4236,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4201,7 +4257,7 @@
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4209,10 +4265,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4223,7 +4279,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4232,21 +4288,21 @@
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>184</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4270,13 +4326,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>260</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4294,39 +4350,39 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>262</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4337,7 +4393,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -4349,16 +4405,20 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -4406,39 +4466,39 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>267</v>
-      </c>
       <c r="AN27" t="s" s="2">
-        <v>262</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4449,7 +4509,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -4458,23 +4518,29 @@
         <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q28" s="2"/>
+      <c r="Q28" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="R28" t="s" s="2">
         <v>78</v>
       </c>
@@ -4518,28 +4584,28 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>274</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -4547,10 +4613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4561,7 +4627,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>78</v>
@@ -4570,16 +4636,16 @@
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4630,13 +4696,13 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
@@ -4651,7 +4717,7 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -4659,10 +4725,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4673,7 +4739,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -4682,18 +4748,20 @@
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -4718,13 +4786,13 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -4742,43 +4810,43 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>78</v>
+        <v>286</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>283</v>
+        <v>183</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4794,20 +4862,18 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -4856,7 +4922,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4868,31 +4934,31 @@
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>78</v>
+        <v>291</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4905,26 +4971,22 @@
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>134</v>
+        <v>294</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
@@ -4972,7 +5034,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4984,16 +5046,16 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>132</v>
+        <v>298</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5001,10 +5063,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5012,10 +5074,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
@@ -5027,13 +5089,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5060,13 +5122,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5084,13 +5146,13 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>78</v>
@@ -5105,7 +5167,7 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5113,10 +5175,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5139,13 +5201,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>214</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5172,13 +5234,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>302</v>
+        <v>78</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>303</v>
+        <v>78</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5196,7 +5258,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>215</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5208,7 +5270,7 @@
         <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -5217,7 +5279,7 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>304</v>
+        <v>216</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5232,14 +5294,14 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
@@ -5251,15 +5313,17 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>243</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>136</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5308,19 +5372,19 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>222</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
@@ -5329,7 +5393,7 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5337,43 +5401,45 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L36" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N36" s="2"/>
+      <c r="N36" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>312</v>
+        <v>144</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5422,19 +5488,19 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -5443,7 +5509,7 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>313</v>
+        <v>132</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5451,10 +5517,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5462,10 +5528,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -5477,13 +5543,13 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>269</v>
+        <v>176</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5510,13 +5576,13 @@
         <v>78</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>78</v>
+        <v>314</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>78</v>
+        <v>315</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
@@ -5534,13 +5600,13 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>78</v>
@@ -5555,9 +5621,459 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/jpcore-r4/feature/wg45-FamilyMember/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/wg45-FamilyMember/StructureDefinition-jp-familymemberhistory.xlsx
@@ -715,7 +715,7 @@
     <t>SiblingOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_FamilyMemberHistory_SiblingOrder}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_FamilyMemberHistory_Relationship_SiblingOrder}
 </t>
   </si>
   <si>
